--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9504</v>
+        <v>4.7601</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2838</v>
+        <v>5.624599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3333999999999999</v>
+        <v>-0.8644999999999998</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2446</v>
+        <v>2.2551</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6208</v>
+        <v>3.7487</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3761</v>
+        <v>-1.4935</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2261</v>
+        <v>4.4536</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3862</v>
+        <v>3.6025</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8399</v>
+        <v>0.8511000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9816</v>
+        <v>-2.1985</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2345</v>
+        <v>0.1461</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.216</v>
+        <v>-2.3446</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4006</v>
+        <v>-2.3368</v>
       </c>
       <c r="R2" t="n">
-        <v>4.4012</v>
+        <v>4.2842</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7046</v>
+        <v>3.6103</v>
       </c>
       <c r="T2" t="n">
-        <v>3.019</v>
+        <v>3.0005</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6856</v>
+        <v>0.6098</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.9994</v>
+        <v>-3.0527</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4392999999999999</v>
+        <v>0.5074</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.4387</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7979</v>
+        <v>2.7727</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0243</v>
+        <v>1.2601</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7736</v>
+        <v>1.5126</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7713</v>
+        <v>2.7682</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0758</v>
+        <v>2.0679</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6955</v>
+        <v>0.7002999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.523</v>
+        <v>3.6457</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3194</v>
+        <v>2.3811</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2036</v>
+        <v>1.2647</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7517</v>
+        <v>-0.8775000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2436</v>
+        <v>-0.3131</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5081</v>
+        <v>-0.5644</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4006</v>
+        <v>2.3369</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.4004</v>
+        <v>-1.3631</v>
       </c>
       <c r="R3" t="n">
-        <v>3.8011</v>
+        <v>3.7</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7743</v>
+        <v>-1.7218</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0179</v>
+        <v>-0.9709000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7564</v>
+        <v>-0.7509</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.08030000000000004</v>
+        <v>-0.05159999999999998</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -721,31 +721,31 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7996</v>
+        <v>1.8316</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7996</v>
+        <v>1.8316</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7996</v>
+        <v>1.8316</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7996</v>
+        <v>1.8316</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2594</v>
+        <v>1.5858</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0723</v>
+        <v>1.9562</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1871</v>
+        <v>-0.3704000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8800000000000001</v>
+        <v>-0.7155</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0125</v>
+        <v>2.085</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8926</v>
+        <v>-2.8005</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9748</v>
+        <v>2.5381</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7936</v>
+        <v>3.1203</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8190000000000001</v>
+        <v>-0.5821000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8548</v>
+        <v>-3.2535</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7810999999999999</v>
+        <v>-1.0353</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0736</v>
+        <v>-2.2182</v>
       </c>
       <c r="P5" t="n">
-        <v>3.601</v>
+        <v>3.5052</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R5" t="n">
-        <v>5.6016</v>
+        <v>5.4526</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.2201</v>
+        <v>-4.1019</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.2603</v>
+        <v>-2.143</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.9598</v>
+        <v>-1.9589</v>
       </c>
       <c r="V5" t="n">
-        <v>2.7585</v>
+        <v>2.8979</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3584</v>
+        <v>3.5085</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8126</v>
+        <v>0.8853</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.804</v>
+        <v>-0.9443</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04870000000000002</v>
+        <v>-0.06259999999999993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7912000000000001</v>
+        <v>0.7927</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3216</v>
+        <v>1.3708</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001800000000000024</v>
+        <v>0.0333</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3198</v>
+        <v>1.3373</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5791999999999999</v>
+        <v>-0.6408</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05050000000000002</v>
+        <v>-0.09599999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5286</v>
+        <v>-0.5448</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9547000000000001</v>
+        <v>-0.9242999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.509</v>
+        <v>-0.4854</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4457</v>
+        <v>-0.4389</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7793999999999999</v>
+        <v>-0.8385</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7793999999999999</v>
+        <v>-0.8385</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2204</v>
+        <v>-0.2114</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7026</v>
+        <v>1.0861</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.923</v>
+        <v>-1.2976</v>
       </c>
       <c r="G7" t="n">
-        <v>1.591</v>
+        <v>1.6095</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8359</v>
+        <v>1.8217</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2449</v>
+        <v>-0.2121</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9722</v>
+        <v>3.2343</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8446</v>
+        <v>3.0149</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1276</v>
+        <v>0.2194</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3812</v>
+        <v>-1.6247</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0087</v>
+        <v>-1.1933</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3725000000000001</v>
+        <v>-0.4315</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0009</v>
+        <v>2.9211</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.272</v>
+        <v>-2.2162</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8489</v>
+        <v>-0.7919</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4231</v>
+        <v>-1.4244</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5399</v>
+        <v>-1.5521</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4204000000000001</v>
+        <v>-0.3826</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5634999999999999</v>
+        <v>-0.6586000000000003</v>
       </c>
       <c r="E8" t="n">
-        <v>0.141</v>
+        <v>0.2932999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7044999999999999</v>
+        <v>-0.9519000000000002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7456</v>
+        <v>0.6645000000000003</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5475000000000001</v>
+        <v>0.4864</v>
       </c>
       <c r="I8" t="n">
-        <v>0.198</v>
+        <v>0.1781000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3614</v>
+        <v>2.4303</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1197</v>
+        <v>1.1495</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2417</v>
+        <v>1.2808</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6158</v>
+        <v>-1.7656</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5722</v>
+        <v>-0.6631</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0437</v>
+        <v>-1.1026</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1096</v>
+        <v>-1.0757</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3399</v>
+        <v>-0.3064</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.7693</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9257</v>
+        <v>-0.8813</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1043</v>
+        <v>-2.6994</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1786</v>
+        <v>1.8181</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3513999999999997</v>
+        <v>-0.3300000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.822</v>
+        <v>1.8453</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1734</v>
+        <v>-2.1754</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2947000000000002</v>
+        <v>0.5197000000000003</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0451</v>
+        <v>1.1675</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7504</v>
+        <v>-0.6477999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6461</v>
+        <v>-0.8498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7769</v>
+        <v>0.6777</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4231</v>
+        <v>-1.5275</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4006</v>
+        <v>-2.3368</v>
       </c>
       <c r="R9" t="n">
-        <v>4.8014</v>
+        <v>4.6737</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9547</v>
+        <v>-1.895</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1779</v>
+        <v>-1.1102</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7768999999999999</v>
+        <v>-0.7847000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0203</v>
+        <v>-0.9930999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8572</v>
+        <v>-1.9316</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1097</v>
+        <v>-2.8966</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7474000000000001</v>
+        <v>0.9649000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0037</v>
+        <v>-2.0701</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1006</v>
+        <v>-1.1832</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9031</v>
+        <v>-0.8868</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4433</v>
+        <v>-1.1677</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9632</v>
+        <v>-1.257</v>
       </c>
       <c r="L10" t="n">
-        <v>0.52</v>
+        <v>0.08950000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5604</v>
+        <v>-0.9025</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1374</v>
+        <v>0.07380000000000003</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.423</v>
+        <v>-0.9762</v>
       </c>
       <c r="P10" t="n">
-        <v>3.601</v>
+        <v>0.779</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-2.3368</v>
       </c>
       <c r="R10" t="n">
-        <v>4.6013</v>
+        <v>3.1158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9348</v>
+        <v>0.02160000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7339</v>
+        <v>0.04890000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6688</v>
+        <v>-0.02740000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5196</v>
+        <v>-0.6620999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1195</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9563</v>
+        <v>-2.0236</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2303</v>
+        <v>-0.799</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2739</v>
+        <v>-1.2245</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.096</v>
+        <v>-4.0703</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2386</v>
+        <v>-3.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.0007</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.365</v>
+        <v>-1.2048</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4088</v>
+        <v>-1.7316</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0438</v>
+        <v>0.5269</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7310000000000001</v>
+        <v>-2.8655</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1702</v>
+        <v>-1.338</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9012</v>
+        <v>-1.5275</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8002</v>
+        <v>3.5052</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4007</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2009</v>
+        <v>4.4789</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01949999999999999</v>
+        <v>-0.8996999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0158</v>
+        <v>0.7687999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003800000000000012</v>
+        <v>-1.6685</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6801999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5196</v>
+        <v>0.6105</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1998</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1287</v>
+        <v>-3.0023</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3651</v>
+        <v>1.9166</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4938</v>
+        <v>-4.918900000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5105</v>
+        <v>2.5634</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9986999999999999</v>
+        <v>0.9369000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5118</v>
+        <v>1.6265</v>
       </c>
       <c r="J12" t="n">
-        <v>5.0779</v>
+        <v>5.4118</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7431</v>
+        <v>1.8525</v>
       </c>
       <c r="L12" t="n">
-        <v>3.3348</v>
+        <v>3.5593</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5674</v>
+        <v>-2.8484</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7444</v>
+        <v>-0.9157000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8229</v>
+        <v>-1.9328</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8002</v>
+        <v>-0.779</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R12" t="n">
-        <v>3.401</v>
+        <v>3.3105</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0392</v>
+        <v>-2.9551</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9711</v>
+        <v>-0.9062</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0681</v>
+        <v>-2.0488</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7996</v>
+        <v>-1.8316</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.2592</v>
+        <v>-3.3321</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2151</v>
+        <v>-7.2094</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6436</v>
+        <v>-3.1274</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5716</v>
+        <v>-4.0819</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.7872</v>
+        <v>-3.763</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4487</v>
+        <v>-2.4698</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3385</v>
+        <v>-1.2932</v>
       </c>
       <c r="J13" t="n">
-        <v>0.644</v>
+        <v>0.9998</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6472</v>
+        <v>-0.4437</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2912</v>
+        <v>1.4435</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.4313</v>
+        <v>-4.7629</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8016</v>
+        <v>-2.0261</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6297</v>
+        <v>-2.7367</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0009</v>
+        <v>-2.9211</v>
       </c>
       <c r="R13" t="n">
-        <v>4.0011</v>
+        <v>3.8948</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3687</v>
+        <v>-2.3089</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2867</v>
+        <v>-1.2062</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0819</v>
+        <v>-1.1027</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0595</v>
+        <v>-2.1111</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0595</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.0509</v>
+        <v>-5.027000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1134</v>
+        <v>5.3314</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.1645</v>
+        <v>-10.3584</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2867</v>
+        <v>1.473400000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>6.676399999999999</v>
+        <v>6.8225</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.3897</v>
+        <v>-5.3488</v>
       </c>
       <c r="J14" t="n">
-        <v>21.38699999999999</v>
+        <v>24.0632</v>
       </c>
       <c r="K14" t="n">
-        <v>11.8341</v>
+        <v>13.5051</v>
       </c>
       <c r="L14" t="n">
-        <v>9.5528</v>
+        <v>10.5584</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.1005</v>
+        <v>-22.5897</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.1579</v>
+        <v>-6.683</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.9424</v>
+        <v>-15.9068</v>
       </c>
       <c r="P14" t="n">
-        <v>19.0054</v>
+        <v>18.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.0059</v>
+        <v>-20.4473</v>
       </c>
       <c r="R14" t="n">
-        <v>40.0114</v>
+        <v>38.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.904</v>
+        <v>-14.4667</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.643</v>
+        <v>-4.102</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.261</v>
+        <v>-10.3647</v>
       </c>
       <c r="V14" t="n">
-        <v>-10.4391</v>
+        <v>-10.5339</v>
       </c>
       <c r="W14" t="n">
-        <v>5.375399999999999</v>
+        <v>5.8175</v>
       </c>
       <c r="X14" t="n">
-        <v>-15.8145</v>
+        <v>-16.3514</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7601</v>
+        <v>3.8305</v>
       </c>
       <c r="E2" t="n">
-        <v>5.624599999999999</v>
+        <v>2.8533</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8644999999999998</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2551</v>
+        <v>-0.7155</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7487</v>
+        <v>2.085</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4935</v>
+        <v>-2.8005</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4536</v>
+        <v>2.5381</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6025</v>
+        <v>3.1203</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8511000000000001</v>
+        <v>-0.5821000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1985</v>
+        <v>-3.2535</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1461</v>
+        <v>-1.0353</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3446</v>
+        <v>-2.2182</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9474</v>
+        <v>3.5052</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3368</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>4.2842</v>
+        <v>5.4526</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6103</v>
+        <v>-1.8572</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0005</v>
+        <v>-1.2459</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6098</v>
+        <v>-0.6113</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.0527</v>
+        <v>2.8979</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5074</v>
+        <v>3.5085</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.56</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7727</v>
+        <v>3.5153</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2601</v>
+        <v>1.7585</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5126</v>
+        <v>1.7569</v>
       </c>
       <c r="G3" t="n">
         <v>2.7682</v>
@@ -688,13 +688,13 @@
         <v>3.7</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7218</v>
+        <v>-0.9792000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9709000000000001</v>
+        <v>-0.4725</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7509</v>
+        <v>-0.5067</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6105</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8316</v>
+        <v>1.843</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8316</v>
+        <v>3.3321</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.4891</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8316</v>
+        <v>2.2551</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6158</v>
+        <v>3.7487</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2158</v>
+        <v>-1.4935</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8316</v>
+        <v>4.4536</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6158</v>
+        <v>3.6025</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2158</v>
+        <v>0.8511000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2.1985</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.1461</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-2.3446</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9474</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3368</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.2842</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.6931</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.7079000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.01479999999999998</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-3.0527</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5074</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5858</v>
+        <v>1.8316</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9562</v>
+        <v>1.8316</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3704000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7155</v>
+        <v>1.8316</v>
       </c>
       <c r="H5" t="n">
-        <v>2.085</v>
+        <v>0.6158</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8005</v>
+        <v>1.2158</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5381</v>
+        <v>1.8316</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1203</v>
+        <v>0.6158</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5821000000000001</v>
+        <v>1.2158</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2535</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0353</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2182</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5052</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5.4526</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.1019</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.143</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.9589</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.8979</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5085</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.059</v>
+        <v>0.7018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8853</v>
+        <v>1.2855</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9443</v>
+        <v>-0.5837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.73</v>
+        <v>1.6095</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06259999999999993</v>
+        <v>1.8217</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7927</v>
+        <v>-0.2121</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3708</v>
+        <v>3.2343</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0333</v>
+        <v>3.0149</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3373</v>
+        <v>0.2194</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6408</v>
+        <v>-1.6247</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09599999999999999</v>
+        <v>-1.1933</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5448</v>
+        <v>-0.4315</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9737</v>
+        <v>1.9474</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9737</v>
+        <v>2.9211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9242999999999999</v>
+        <v>-1.303</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4854</v>
+        <v>-0.5924999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4389</v>
+        <v>-0.7103999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8385</v>
+        <v>-1.5521</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3826</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8385</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2114</v>
+        <v>0.3126</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0861</v>
+        <v>0.985</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2976</v>
+        <v>-0.6723</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6095</v>
+        <v>0.73</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8217</v>
+        <v>-0.06259999999999993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2121</v>
+        <v>0.7927</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2343</v>
+        <v>1.3708</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0149</v>
+        <v>0.0333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2194</v>
+        <v>1.3373</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6247</v>
+        <v>-0.6408</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1933</v>
+        <v>-0.09599999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4315</v>
+        <v>-0.5448</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9474</v>
+        <v>0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9211</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2162</v>
+        <v>-0.5526</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7919</v>
+        <v>-0.3858</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4244</v>
+        <v>-0.1668</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5521</v>
+        <v>-0.8385</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3826</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1695</v>
+        <v>-0.8385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6586000000000003</v>
+        <v>-0.3264</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2932999999999999</v>
+        <v>-2.5001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9519000000000002</v>
+        <v>2.1736</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6645000000000003</v>
+        <v>-0.3300000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4864</v>
+        <v>1.8453</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1781000000000001</v>
+        <v>-2.1754</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4303</v>
+        <v>0.5197000000000003</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1495</v>
+        <v>1.1675</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2808</v>
+        <v>-0.6477999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7656</v>
+        <v>-0.8498</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6631</v>
+        <v>0.6777</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1026</v>
+        <v>-1.5275</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9737</v>
+        <v>2.3368</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1684</v>
+        <v>-2.3368</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1421</v>
+        <v>4.6737</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0757</v>
+        <v>-1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3064</v>
+        <v>-0.9108999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7693</v>
+        <v>-0.4292</v>
       </c>
       <c r="V8" t="n">
+        <v>-0.9930999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="X8" t="n">
         <v>-1.2211</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.6621</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8813</v>
+        <v>-0.4143000000000003</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6994</v>
+        <v>0.2934000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8181</v>
+        <v>-0.7077</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3300000000000001</v>
+        <v>0.6645000000000003</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8453</v>
+        <v>0.4864</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1754</v>
+        <v>0.1781000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5197000000000003</v>
+        <v>2.4303</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1675</v>
+        <v>1.1495</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6477999999999999</v>
+        <v>1.2808</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8498</v>
+        <v>-1.7656</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6777</v>
+        <v>-0.6631</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5275</v>
+        <v>-1.1026</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3368</v>
+        <v>0.9737</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3368</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>4.6737</v>
+        <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.895</v>
+        <v>-0.8316</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1102</v>
+        <v>-0.3064</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7847000000000001</v>
+        <v>-0.5252</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9930999999999999</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2279</v>
+        <v>-0.6621</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2211</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9316</v>
+        <v>-1.0681</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8966</v>
+        <v>2.6143</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9649000000000001</v>
+        <v>-3.6825</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0701</v>
+        <v>2.5634</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1832</v>
+        <v>0.9369000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8868</v>
+        <v>1.6265</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1677</v>
+        <v>5.4118</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.257</v>
+        <v>1.8525</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08950000000000001</v>
+        <v>3.5593</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9025</v>
+        <v>-2.8484</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07380000000000003</v>
+        <v>-0.9157000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9762</v>
+        <v>-1.9328</v>
       </c>
       <c r="P10" t="n">
-        <v>0.779</v>
+        <v>-0.779</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3368</v>
+        <v>-4.0895</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1158</v>
+        <v>3.3105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02160000000000001</v>
+        <v>-1.021</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04890000000000001</v>
+        <v>-0.2085</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.02740000000000001</v>
+        <v>-0.8124</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6620999999999999</v>
+        <v>-1.8316</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.5005</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2211</v>
+        <v>-3.3321</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0236</v>
+        <v>-1.6357</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.799</v>
+        <v>-1.3972</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2245</v>
+        <v>-0.2386</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0703</v>
@@ -1312,13 +1312,13 @@
         <v>4.4789</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8996999999999999</v>
+        <v>-0.5116999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7687999999999999</v>
+        <v>0.1708</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6685</v>
+        <v>-0.6825000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5590000000000001</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0023</v>
+        <v>-2.6967</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9166</v>
+        <v>-3.4946</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.918900000000001</v>
+        <v>0.7980000000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5634</v>
+        <v>-2.0701</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9369000000000001</v>
+        <v>-1.1832</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6265</v>
+        <v>-0.8868</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4118</v>
+        <v>-1.1677</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8525</v>
+        <v>-1.257</v>
       </c>
       <c r="L12" t="n">
-        <v>3.5593</v>
+        <v>0.08950000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8484</v>
+        <v>-0.9025</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9157000000000001</v>
+        <v>0.07380000000000003</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9328</v>
+        <v>-0.9762</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.779</v>
+        <v>0.779</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0895</v>
+        <v>-2.3368</v>
       </c>
       <c r="R12" t="n">
-        <v>3.3105</v>
+        <v>3.1158</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.9551</v>
+        <v>-0.7434000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9062</v>
+        <v>-0.5490999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0488</v>
+        <v>-0.1942</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8316</v>
+        <v>-0.6620999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5005</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.3321</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2094</v>
+        <v>-5.6046</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1274</v>
+        <v>-2.2304</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0819</v>
+        <v>-3.3743</v>
       </c>
       <c r="G13" t="n">
         <v>-3.763</v>
@@ -1468,13 +1468,13 @@
         <v>3.8948</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3089</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2062</v>
+        <v>-0.3091</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1027</v>
+        <v>-0.395</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1111</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.027000000000001</v>
+        <v>0.2890000000000015</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3314</v>
+        <v>5.331400000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.3584</v>
+        <v>-5.0424</v>
       </c>
       <c r="G14" t="n">
         <v>1.473400000000002</v>
@@ -1546,13 +1546,13 @@
         <v>38.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.4667</v>
+        <v>-9.150700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.102</v>
+        <v>-4.101999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.3647</v>
+        <v>-5.0485</v>
       </c>
       <c r="V14" t="n">
         <v>-10.5339</v>
